--- a/output/laminas_comunales/comunal_o_ocup_a_2019_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2019_coquimbo.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,211 +375,1576 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="C2">
-        <v>38.2936820983887</v>
+        <v>57.5697364807129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Illapel</t>
         </is>
       </c>
       <c r="C3">
-        <v>37.9832191467285</v>
+        <v>57.5400886535645</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="C4">
-        <v>37.8613090515137</v>
+        <v>57.2943725585938</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="C5">
-        <v>37.3693161010742</v>
+        <v>57.031867980957</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="C6">
-        <v>37.2586059570312</v>
+        <v>56.8338851928711</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="C7">
-        <v>36.3995323181152</v>
+        <v>56.2806015014649</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Illapel</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="C8">
-        <v>35.3779983520508</v>
+        <v>55.8839721679688</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="C9">
-        <v>34.0051345825195</v>
+        <v>55.5772438049316</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Andacollo</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="C10">
-        <v>33.3904800415039</v>
+        <v>54.2387771606445</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>Andacollo</t>
         </is>
       </c>
       <c r="C11">
-        <v>32.1047515869141</v>
+        <v>53.8542556762695</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Combarbalá</t>
         </is>
       </c>
       <c r="C12">
-        <v>29.9926128387451</v>
+        <v>53.350456237793</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="C13">
-        <v>28.7552280426025</v>
+        <v>50.6604118347168</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>La Higuera</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="C14">
-        <v>26.0194759368896</v>
+        <v>49.9340858459473</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>49.1586151123047</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>48.0050926208496</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>47.5783538818359</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>47.3511810302734</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>47.2293701171875</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>47.1737060546875</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>47.0101203918457</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>46.81201171875</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>46.6935157775879</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>46.2575759887695</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>45.9739723205566</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>45.6818237304688</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>45.676700592041</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>45.6326866149902</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>44.7965087890625</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>44.7502708435059</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>44.5931930541992</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>4202</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Canela</t>
         </is>
       </c>
-      <c r="C15">
+      <c r="C32">
+        <v>43.543643951416</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>43.2709274291992</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>43.0540657043457</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>42.7837295532227</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>42.7305679321289</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>40.3553161621094</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>39.9463806152344</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>39.0870933532715</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>38.2936820983887</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>37.9832191467285</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>37.8613090515137</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>37.3693161010742</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>37.3349227905273</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>37.2586059570312</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>36.8426087614752</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>36.5416564941406</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>36.3995323181152</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>35.3779983520508</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>34.0051345825195</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>33.6540718078613</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>33.3970794677734</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>33.3904800415039</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>33.2632827758789</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>33.0988121032715</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>32.8182258605957</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>32.5515785217285</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>32.2225646972656</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>32.1047515869141</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>31.4680862426758</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>31.3961448669434</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>31.2695388793945</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>31.0346775054932</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>30.5846252441406</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>30.4373378753662</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>30.2446479797363</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>30.0920372009277</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>29.9926128387451</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>29.9168300628662</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>29.1062793731689</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>29.0406856536865</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>28.8333339691162</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>28.7836837768555</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>28.7552280426025</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>28.7545795440674</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>28.6642932891846</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>28.482889175415</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>26.852575302124</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>26.6765880584717</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>26.580472946167</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>26.0194759368896</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>25.708890914917</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>25.0230846405029</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C84">
         <v>24.2407207489014</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>23.879301071167</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>23.7280960083008</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>23.4859752655029</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>22.1558151245117</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>20.5665187835693</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>19.2797870635986</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>17.6473236083984</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>11.2593679428101</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>10.1260528564453</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>10.0101900100708</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>9.924203872680661</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>9.66307353973389</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>9.631306648254389</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>9.491945266723629</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>9.244743347167971</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>8.2219352722168</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>7.98555374145508</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>7.88005590438843</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>7.72058820724487</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>7.24548435211182</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>6.90535879135132</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>5.76643419265747</v>
       </c>
     </row>
   </sheetData>
